--- a/artfynd/A 40686-2024 artfynd.xlsx
+++ b/artfynd/A 40686-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246638</v>
       </c>
       <c r="B2" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40686-2024 artfynd.xlsx
+++ b/artfynd/A 40686-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246638</v>
       </c>
       <c r="B2" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40686-2024 artfynd.xlsx
+++ b/artfynd/A 40686-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246638</v>
       </c>
       <c r="B2" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40686-2024 artfynd.xlsx
+++ b/artfynd/A 40686-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246638</v>
       </c>
       <c r="B2" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40686-2024 artfynd.xlsx
+++ b/artfynd/A 40686-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246638</v>
       </c>
       <c r="B2" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40686-2024 artfynd.xlsx
+++ b/artfynd/A 40686-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246638</v>
       </c>
       <c r="B2" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
